--- a/good_revenue_explanation.xlsx
+++ b/good_revenue_explanation.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyson.king\Documents\testing_work\comps_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A387F8-CB92-4376-BAA9-8214AD5CA451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924DACA5-0748-41B0-A72A-D72B0715AF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98D154FB-6552-40E8-BDB7-033A2476C63E}"/>
   </bookViews>
   <sheets>
     <sheet name="Phoenix - Cortland at Raven" sheetId="1" r:id="rId1"/>
     <sheet name="Nashville - Nations" sheetId="2" r:id="rId2"/>
+    <sheet name="Atlanta - 1000 Spalding" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
   <si>
     <t>Good</t>
   </si>
@@ -133,6 +134,39 @@
   </si>
   <si>
     <t>The Shay</t>
+  </si>
+  <si>
+    <t>45Eighty Dunwoody</t>
+  </si>
+  <si>
+    <t>Aventura Dunwoody</t>
+  </si>
+  <si>
+    <t>Celebration at Sandy Springs</t>
+  </si>
+  <si>
+    <t>Dunwoody Gables</t>
+  </si>
+  <si>
+    <t>Dunwoody Ridge</t>
+  </si>
+  <si>
+    <t>Hawthorne Gates</t>
+  </si>
+  <si>
+    <t>The Adair Apartment Homes</t>
+  </si>
+  <si>
+    <t>The Carlyle at Perimeter</t>
+  </si>
+  <si>
+    <t>The Reserve at Ridgewood</t>
+  </si>
+  <si>
+    <t>1000 Spalding</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -140,7 +174,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="175" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -187,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -195,7 +229,7 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -204,21 +238,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <color theme="9" tint="-0.24994659260841701"/>
@@ -227,16 +254,6 @@
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.24994659260841701"/>
       </font>
     </dxf>
     <dxf>
@@ -266,6 +283,11 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="9" tint="-0.24994659260841701"/>
       </font>
     </dxf>
@@ -276,7 +298,32 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="9"/>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
       </font>
     </dxf>
   </dxfs>
@@ -296,14 +343,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1381125</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>19853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1619250</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>114740</xdr:rowOff>
     </xdr:to>
@@ -328,8 +375,101 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="4020353"/>
+          <a:off x="6762750" y="4020353"/>
           <a:ext cx="6315075" cy="2952387"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>32763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1274683</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32BC4773-DDE9-4445-7DA7-71A1B82E0999}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4033263"/>
+          <a:ext cx="6656308" cy="1596012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>426339</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE29C26E-AE38-4DEF-8AB7-F062F42D5A0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12620625" y="390525"/>
+          <a:ext cx="5045964" cy="2867025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -345,23 +485,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1381125</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>19853</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1619250</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>114740</xdr:rowOff>
+      <xdr:rowOff>104412</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DDAAB23-716A-4DC1-837D-5FEAE3D29AD9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F344051-93D6-473C-9906-6D3E96D81AB1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -377,8 +517,244 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="4020353"/>
+          <a:off x="6762750" y="4010025"/>
           <a:ext cx="6315075" cy="2952387"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>22435</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1274683</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>94447</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F651D158-C688-43B6-9A99-2FE838D770FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4022935"/>
+          <a:ext cx="6656308" cy="1596012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>445389</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{685F08DF-D6DE-4581-A4F2-E16241FBE4AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12639675" y="219075"/>
+          <a:ext cx="5045964" cy="2867025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1381125</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>104412</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B83B945F-F1B1-4F4B-86BF-91B777452A6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6762750" y="4010025"/>
+          <a:ext cx="6315075" cy="2952387"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>22435</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1274683</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>94447</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AE4FE9F-5DC4-4798-91AB-7A87D806EA09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4022935"/>
+          <a:ext cx="6656308" cy="1596012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>249279</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>10839</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>418443</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>20364</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E33885A-0842-D7B0-76A5-3DA0E06D79BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12618641" y="201339"/>
+          <a:ext cx="5056474" cy="2867025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -823,7 +1199,7 @@
       <c r="E7" s="3">
         <v>2.3297649854051999E-2</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="1"/>
@@ -847,7 +1223,7 @@
       <c r="E8" s="3">
         <v>-1.6305156191647099E-2</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G8" s="1">
@@ -873,7 +1249,7 @@
       <c r="E9" s="3">
         <v>-2.41700877010722E-2</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="1">
@@ -899,7 +1275,7 @@
       <c r="E10" s="3">
         <v>-8.5131207542145704E-2</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G10" s="1">
@@ -925,7 +1301,7 @@
       <c r="E11" s="3">
         <v>-3.3486207125043202E-2</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G11" s="1">
@@ -951,7 +1327,7 @@
       <c r="E12" s="3">
         <v>1.43250437161603E-2</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G12" s="1">
@@ -977,7 +1353,7 @@
       <c r="E13" s="3">
         <v>-2.09544410063724E-2</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G13" s="1">
@@ -1003,7 +1379,7 @@
       <c r="E14" s="3">
         <v>-4.1306015245476002E-2</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G14" s="1">
@@ -1029,7 +1405,7 @@
       <c r="E15" s="3">
         <v>-8.5421673084467895E-2</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G15" s="1">
@@ -1055,7 +1431,7 @@
       <c r="E16" s="3">
         <v>-8.7336618800106305E-2</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G16" s="1">
@@ -1081,7 +1457,7 @@
       <c r="E17" s="3">
         <v>-7.87558760258915E-2</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G17" s="1">
@@ -1104,7 +1480,7 @@
       <c r="E18" s="3">
         <v>-5.2022351995073303E-2</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G18" s="1">
@@ -1127,7 +1503,7 @@
       <c r="E19" s="3">
         <v>-5.3989432665899603E-2</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G19" s="1">
@@ -1150,7 +1526,7 @@
       <c r="E20" s="3">
         <v>-5.4527005601109499E-2</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G20" s="1">
@@ -1173,7 +1549,7 @@
       <c r="E21" s="3">
         <v>-5.13842722898094E-2</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G21" s="1"/>
@@ -1183,18 +1559,18 @@
     <mergeCell ref="A1:M4"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F1048576">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"Poor"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"Good"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G21">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1321,7 +1697,7 @@
       <c r="E7" s="3">
         <v>0.32073358902010102</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G7" s="1"/>
@@ -1345,7 +1721,7 @@
       <c r="E8" s="3">
         <v>0.22041259286696299</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G8" s="1">
@@ -1371,7 +1747,7 @@
       <c r="E9" s="3">
         <v>0.15246001446245</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="1">
@@ -1397,7 +1773,7 @@
       <c r="E10" s="3">
         <v>0.15082899300814501</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G10" s="1">
@@ -1423,7 +1799,7 @@
       <c r="E11" s="3">
         <v>0.28656426777851102</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G11" s="1">
@@ -1449,7 +1825,7 @@
       <c r="E12" s="3">
         <v>0.33866802743434898</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G12" s="1">
@@ -1475,7 +1851,7 @@
       <c r="E13" s="3">
         <v>0.35528383489223397</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G13" s="1">
@@ -1501,7 +1877,7 @@
       <c r="E14" s="3">
         <v>0.312650317305049</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G14" s="1">
@@ -1527,7 +1903,7 @@
       <c r="E15" s="3">
         <v>0.32754773635833001</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G15" s="1">
@@ -1553,7 +1929,7 @@
       <c r="E16" s="3">
         <v>0.29340085571219898</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G16" s="1">
@@ -1579,7 +1955,7 @@
       <c r="E17" s="3">
         <v>0.25130830801278298</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G17" s="1">
@@ -1602,7 +1978,7 @@
       <c r="E18" s="3">
         <v>0.20388280069936099</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G18" s="1">
@@ -1625,7 +2001,7 @@
       <c r="E19" s="3">
         <v>0.20560870319173899</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G19" s="1">
@@ -1648,7 +2024,7 @@
       <c r="E20" s="3">
         <v>0.25519036916161603</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G20" s="1">
@@ -1671,7 +2047,7 @@
       <c r="E21" s="3">
         <v>0.24268259844180001</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G21" s="1"/>
@@ -1681,6 +2057,507 @@
     <mergeCell ref="A1:M4"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F1048576">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+      <formula>"Poor"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+      <formula>"Good"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G21">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3165B06A-0A28-494F-B144-67A799FC17AC}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="31.140625" customWidth="1"/>
+    <col min="13" max="13" width="27.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45292</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="3">
+        <v>1.62756804896887</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.40047215023982402</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45323</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1.59042008805242</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.45034654777486299</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3469.73000000003</v>
+      </c>
+      <c r="M8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>45352</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.5577133254879501</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.41852273795143202</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>-3690.6100000000401</v>
+      </c>
+      <c r="M9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>45383</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.5397540995735299</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.399244143871541</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4370.96000000002</v>
+      </c>
+      <c r="M10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45413</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.51817541798001</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.37935620138676501</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>-5178.1500000000196</v>
+      </c>
+      <c r="M11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>45444</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.53144178308028</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.41526970278191699</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10351.120000000001</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>45474</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.5337867117892601</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.41019607355770499</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>-8782.0300000000207</v>
+      </c>
+      <c r="M13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>45505</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1.5060464966279701</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.39277462989470502</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>3867.1599999999698</v>
+      </c>
+      <c r="M14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>45536</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.5089802587310699</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.38177004368872097</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>-2695.9499999999498</v>
+      </c>
+      <c r="M15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45566</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1.52206733035933</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.39990458192521799</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>11891.049999999899</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45597</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.5234789172485099</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.41478197548804802</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>-15709.77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45627</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1.46798037352657</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.37079450481190901</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>-3891.5299999999602</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1.4128569696924</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.308020601432547</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>6385.0899999999601</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45689</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1.4204560747463399</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.29412320046331403</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>-25845.4199999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>45717</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1.48189092923754</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.34908951136921301</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F5:F6 F22:F1048576">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+      <formula>"Poor"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"Good"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F21">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Poor"</formula>
     </cfRule>
@@ -1689,10 +2566,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G21">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
